--- a/data/trans_orig/IQ17B_M_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,35; 11,78</t>
+          <t>6,18; 11,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,92</t>
+          <t>5,04; 7,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 13,0</t>
+          <t>6,05; 12,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,34</t>
+          <t>6,31; 10,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,74</t>
+          <t>6,07; 10,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,05</t>
+          <t>4,95; 8,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 12,49</t>
+          <t>7,31; 12,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,59; 12,32</t>
+          <t>7,57; 12,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,15</t>
+          <t>6,6; 9,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 7,33</t>
+          <t>5,26; 7,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 11,3</t>
+          <t>7,48; 11,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 10,58</t>
+          <t>7,31; 10,57</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,13</t>
+          <t>5,64; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 5,95</t>
+          <t>4,79; 5,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,64</t>
+          <t>5,45; 6,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 9,55</t>
+          <t>7,8; 9,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,17</t>
+          <t>5,84; 7,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,11</t>
+          <t>5,51; 7,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 7,07</t>
+          <t>5,77; 7,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 12,51</t>
+          <t>8,61; 12,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 6,93</t>
+          <t>5,91; 6,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,3</t>
+          <t>5,27; 6,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 6,62</t>
+          <t>5,74; 6,63</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 10,5</t>
+          <t>8,51; 10,68</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,36</t>
+          <t>5,04; 7,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 4,97</t>
+          <t>3,79; 4,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 6,39</t>
+          <t>4,85; 6,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,92; 8,16</t>
+          <t>5,97; 7,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,24</t>
+          <t>4,51; 6,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 6,11</t>
+          <t>4,5; 6,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,61</t>
+          <t>4,77; 6,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 9,97</t>
+          <t>6,87; 9,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,44</t>
+          <t>5,08; 6,45</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,36; 5,34</t>
+          <t>4,38; 5,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,23</t>
+          <t>5,03; 6,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,55; 8,48</t>
+          <t>6,67; 8,67</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,06</t>
+          <t>5,83; 7,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,67</t>
+          <t>4,81; 5,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,65</t>
+          <t>5,62; 6,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,98</t>
+          <t>7,55; 8,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 6,9</t>
+          <t>5,85; 6,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,58</t>
+          <t>5,42; 6,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,97</t>
+          <t>5,9; 6,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,4</t>
+          <t>8,48; 11,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,96; 6,86</t>
+          <t>6,0; 6,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,05</t>
+          <t>5,25; 5,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,93; 6,67</t>
+          <t>5,91; 6,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,18; 9,71</t>
+          <t>8,21; 9,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Estudios-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función del número de meses de su última consulta al médico (tasa de respuesta: 91,3%)</t>
+          <t>Tiempo medio en meses desde la última consulta médica por algo que le pasaba a su hijo/a (tasa de respuesta: 91,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,54 +648,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7,62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,06</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9,68</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,18</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,9</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,62</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>9,1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7,87</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>6,18</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,54</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>8,99</t>
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,9</t>
+          <t>9,4</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,61</t>
+          <t>6,03; 10,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,99</t>
+          <t>5,01; 8,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 12,87</t>
+          <t>7,27; 12,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,44</t>
+          <t>7,73; 12,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 10,27</t>
+          <t>6,16; 11,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,09</t>
+          <t>4,97; 7,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 12,01</t>
+          <t>6,15; 13,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 12,31</t>
+          <t>7,32; 11,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,6; 9,92</t>
+          <t>6,47; 9,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,24</t>
+          <t>5,29; 7,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,3</t>
+          <t>7,37; 11,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,57</t>
+          <t>8,0; 11,12</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,45</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,14</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6,36</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,07</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>6,22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,27</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>5,99</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,5</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,45</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,14</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>8,77</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>9,43</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,21</t>
+          <t>5,88; 7,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,96</t>
+          <t>5,46; 7,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,66</t>
+          <t>5,73; 7,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,8; 9,58</t>
+          <t>8,86; 12,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 7,22</t>
+          <t>5,61; 7,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 7,14</t>
+          <t>4,82; 6,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 7,08</t>
+          <t>5,45; 6,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 12,28</t>
+          <t>7,91; 9,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,84</t>
+          <t>5,88; 6,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,33</t>
+          <t>5,31; 6,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 6,63</t>
+          <t>5,78; 6,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,68</t>
+          <t>8,68; 10,56</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,54</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,26</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,33</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5,63</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,88</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,54</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,65</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 7,3</t>
+          <t>4,54; 6,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 4,96</t>
+          <t>4,5; 6,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 6,45</t>
+          <t>4,84; 6,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,87</t>
+          <t>7,07; 10,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,17</t>
+          <t>5,14; 7,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,08</t>
+          <t>3,75; 4,89</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 6,67</t>
+          <t>4,87; 6,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 9,72</t>
+          <t>6,02; 8,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,45</t>
+          <t>5,05; 6,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,44</t>
+          <t>4,4; 5,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,24</t>
+          <t>5,0; 6,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 8,67</t>
+          <t>6,8; 8,84</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,92</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,41</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,38</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,19</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,11</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,32</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>9,03</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,15</t>
+          <t>5,83; 6,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,72</t>
+          <t>5,41; 6,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,64</t>
+          <t>5,91; 6,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,97</t>
+          <t>8,66; 11,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,85; 6,93</t>
+          <t>5,86; 7,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,61</t>
+          <t>4,77; 5,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 6,98</t>
+          <t>5,65; 6,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,31</t>
+          <t>7,81; 9,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 6,82</t>
+          <t>5,96; 6,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,25; 5,99</t>
+          <t>5,27; 6,0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,65</t>
+          <t>5,89; 6,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 9,77</t>
+          <t>8,42; 9,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>7,62</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,06</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9,68</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,12</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,9</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9,1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7,87</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8,99</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,4</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>7.622218687387508</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.184166825688751</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>9.056453658204726</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>9.68452232514769</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>8.122244079699451</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>6.181116375873817</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>8.895621037534571</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>9.095988926171845</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7.867424681132597</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>6.182555360271111</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>8.990065007934913</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>9.398574541790987</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6,03; 10,5</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,01; 8,24</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7,27; 12,15</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7,73; 12,53</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>6,16; 11,81</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,97; 7,9</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>6,15; 13,02</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7,32; 11,0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>6,47; 9,99</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5,29; 7,23</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>7,37; 11,05</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>8,0; 11,12</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>6.025271838323424</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5.014606409941877</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>7.268203559250387</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>7.734724814952926</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>6.160021750397632</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4.968159769184201</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>6.149614858908337</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>7.318888174661764</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>6.465236577355955</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>5.291180598637507</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>7.365126002401457</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>8.004492668029375</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.49672662219038</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.239572234568831</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>12.15191263617571</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12.52742090194225</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>11.8057648749939</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>7.899262727876926</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>13.01704390043983</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>10.99854845115315</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>9.987563188458481</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>7.230323726997582</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>11.04613013598609</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>11.11990939473892</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,45</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,14</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6,36</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,07</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,22</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,27</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,99</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8,77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>6,17</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>9,43</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5,88; 7,28</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,46; 7,13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5,73; 7,09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8,86; 12,07</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,61; 7,15</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,82; 6,06</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,45; 6,65</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7,91; 9,8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5,88; 6,88</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5,31; 6,38</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5,78; 6,64</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,68; 10,56</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.450195694424682</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.137507213473674</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>6.356388565564313</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>10.06650860463669</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>6.222166182059002</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5.272968687602003</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.991775133584165</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>8.769858987190368</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>6.338415488680975</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>5.719791514096313</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>6.173215804843885</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>9.431539716677412</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,28</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,54</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8,26</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,63</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5,67</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>4,81</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5,58</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>7,65</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>5.880417119206046</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5.464630600335114</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>5.734674781337384</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>8.859066547332009</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>5.607775596546819</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>4.821557280666271</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>5.453257431205063</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>7.913292462947306</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5.877815842108636</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>5.311296212846036</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>5.780069444520596</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>8.676736923477129</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,54; 6,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,5; 6,16</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4,84; 6,66</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7,07; 10,54</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,14; 7,32</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>3,75; 4,89</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,87; 6,41</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>6,02; 8,24</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5,05; 6,56</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>4,4; 5,42</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>5,0; 6,21</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,8; 8,84</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7.277289655426203</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.12687153621377</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.094159256321379</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>12.07420786246955</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>7.149549395543757</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>6.056697209964552</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>6.645488871106068</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>9.795911319034678</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>6.877230263668867</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>6.376533819213919</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>6.636525961664073</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>10.55766790250037</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6,32</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,92</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9,63</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,38</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,19</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,11</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8,4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5,57</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6,26</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,03</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.283561712014776</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.224502623140382</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5.535136192338745</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>8.260184028288915</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.001406927261854</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>4.332431625545442</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.628414451018234</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>7.009234928805749</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5.667051592345272</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>4.814033690377961</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>5.579527289640108</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>7.647483765186196</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>5,83; 6,96</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,41; 6,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,91; 6,95</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8,66; 11,12</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,86; 7,04</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,77; 5,69</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,65; 6,67</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>7,81; 9,31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5,96; 6,76</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>5,27; 6,0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5,89; 6,62</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,42; 9,85</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>4.542400294580165</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4.497799409413028</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>4.842346519062555</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>7.074313899226329</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>5.139864761805463</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>3.75016320417902</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4.871431159272556</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>6.016748965932606</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5.050791066931675</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>4.400115920981191</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>5.00313196339233</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>6.800540198947036</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.319712182671535</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.159261499754633</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.659542616528023</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>10.53695590364356</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>7.31765522739506</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.88603907131893</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>6.405225715929756</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>8.244205886303421</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6.564553607319533</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>5.41595137316915</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>6.206851610754647</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>8.840847103448853</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6.321829052082752</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.920159964719862</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>6.409716475155274</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>9.626501739644102</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>6.375251424384292</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>5.187268300719906</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>6.112714209750386</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>8.398583892350468</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6.348587074309184</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>5.56588720416683</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>6.264766149745702</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>9.025558523926851</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5.831234468004642</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>5.41083557341736</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5.910952614123493</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>8.657597770561066</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>5.861214706991507</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>4.770470046331008</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>5.650762711975142</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>7.808656220437176</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5.963267654787542</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>5.269366589939671</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>5.892573012397035</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>8.421109842676843</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.9634284573421</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.609449962846966</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.945046292950738</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>11.115460547874</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>7.043998315793036</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>5.687531049695793</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>6.669640298919225</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>9.311771362622764</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6.763126297223796</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>6.003003915551291</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>6.616622732066278</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>9.852484715821992</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
